--- a/employment_xlsx/PECH_HR_MASTER_DASHBOARD.xlsx
+++ b/employment_xlsx/PECH_HR_MASTER_DASHBOARD.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -70,6 +70,34 @@
       <i val="1"/>
       <color rgb="00999999"/>
       <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000099CC"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="00F5A623"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00888888"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00E8F4F8"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00AAAAAA"/>
+      <sz val="7"/>
     </font>
   </fonts>
   <fills count="9">
@@ -148,7 +176,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -191,6 +219,21 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -265,6 +308,36 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="628650"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -554,8 +627,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -568,45 +642,31 @@
     <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="6" customHeight="1">
-      <c r="A1" s="1" t="inlineStr"/>
-      <c r="B1" s="1" t="inlineStr"/>
-      <c r="C1" s="1" t="inlineStr"/>
-      <c r="D1" s="1" t="inlineStr"/>
-      <c r="E1" s="1" t="inlineStr"/>
-      <c r="F1" s="1" t="inlineStr"/>
-      <c r="G1" s="1" t="inlineStr"/>
-      <c r="H1" s="1" t="inlineStr"/>
-    </row>
-    <row r="2" ht="36" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="20" t="inlineStr">
         <is>
           <t>PECH GROUP HOLDINGS LTD</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="n"/>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>PECH HR MASTER DASHBOARD</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="n"/>
-    </row>
-    <row r="4" ht="4" customHeight="1">
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="21" t="inlineStr">
+        <is>
+          <t>Technology &amp; Infrastructure Enablers for People</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="4" customHeight="1">
+      <c r="A3" s="1" t="n"/>
+      <c r="B3" s="1" t="n"/>
+      <c r="C3" s="1" t="n"/>
+      <c r="D3" s="1" t="n"/>
+      <c r="E3" s="1" t="n"/>
+      <c r="F3" s="1" t="n"/>
+      <c r="G3" s="1" t="n"/>
+      <c r="H3" s="1" t="n"/>
+    </row>
+    <row r="4" ht="2" customHeight="1">
       <c r="A4" s="5" t="n"/>
       <c r="B4" s="5" t="n"/>
       <c r="C4" s="5" t="n"/>
@@ -616,238 +676,122 @@
       <c r="G4" s="5" t="n"/>
       <c r="H4" s="5" t="n"/>
     </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>Lagos, Nigeria  |  pechgroupholdings.tech  |  Confidential</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="8" customHeight="1"/>
+    <row r="7" ht="8" customHeight="1">
+      <c r="A7" s="1" t="inlineStr"/>
+      <c r="B7" s="1" t="inlineStr"/>
+      <c r="C7" s="1" t="inlineStr"/>
+      <c r="D7" s="1" t="inlineStr"/>
+      <c r="E7" s="1" t="inlineStr"/>
+      <c r="F7" s="1" t="inlineStr"/>
+      <c r="G7" s="1" t="inlineStr"/>
+      <c r="H7" s="1" t="inlineStr"/>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>PECH GROUP HOLDINGS LTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>PECH HR MASTER DASHBOARD</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n"/>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>Lagos, Nigeria  |  pechgroupholdings.tech  |  Employment Documents Overview  |  CONFIDENTIAL</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="3" t="n"/>
-      <c r="H5" s="3" t="n"/>
-    </row>
-    <row r="6" ht="4" customHeight="1">
-      <c r="A6" s="5" t="n"/>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="1" t="n"/>
-      <c r="F6" s="1" t="n"/>
-      <c r="G6" s="1" t="n"/>
-      <c r="H6" s="1" t="n"/>
-    </row>
-    <row r="7" ht="8" customHeight="1"/>
-    <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n"/>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="1" t="n"/>
+      <c r="F12" s="1" t="n"/>
+      <c r="G12" s="1" t="n"/>
+      <c r="H12" s="1" t="n"/>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  DOCUMENT INDEX &amp; STATUS</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n"/>
-      <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="n"/>
-      <c r="E8" s="8" t="n"/>
-      <c r="F8" s="8" t="n"/>
-      <c r="G8" s="8" t="n"/>
-      <c r="H8" s="8" t="n"/>
-    </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>Document Name</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>Total Records</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E15" s="9" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="F9" s="9" t="inlineStr">
+      <c r="F15" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="G15" s="9" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="H9" s="9" t="inlineStr">
+      <c r="H15" s="9" t="inlineStr">
         <is>
           <t>Google Sheets Link</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>Full-Time Employment Contract</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>Contract</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="n"/>
-      <c r="E10" s="10" t="n"/>
-      <c r="F10" s="10" t="n"/>
-      <c r="G10" s="10" t="n"/>
-      <c r="H10" s="11" t="inlineStr">
-        <is>
-          <t>(paste Google Sheets URL here)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>Contract Worker Agreement</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>Contract</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="12" t="n"/>
-      <c r="F11" s="12" t="n"/>
-      <c r="G11" s="12" t="n"/>
-      <c r="H11" s="13" t="inlineStr">
-        <is>
-          <t>(paste Google Sheets URL here)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>Internship Agreement</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>Contract</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="n"/>
-      <c r="E12" s="10" t="n"/>
-      <c r="F12" s="10" t="n"/>
-      <c r="G12" s="10" t="n"/>
-      <c r="H12" s="11" t="inlineStr">
-        <is>
-          <t>(paste Google Sheets URL here)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>Office Marketer Agreement</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>Contract</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="n"/>
-      <c r="E13" s="12" t="n"/>
-      <c r="F13" s="12" t="n"/>
-      <c r="G13" s="12" t="n"/>
-      <c r="H13" s="13" t="inlineStr">
-        <is>
-          <t>(paste Google Sheets URL here)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>Commission Marketer Agreement</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>Contract</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="n"/>
-      <c r="E14" s="10" t="n"/>
-      <c r="F14" s="10" t="n"/>
-      <c r="G14" s="10" t="n"/>
-      <c r="H14" s="11" t="inlineStr">
-        <is>
-          <t>(paste Google Sheets URL here)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>Installer Agreement</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>Contract</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="n"/>
-      <c r="E15" s="12" t="n"/>
-      <c r="F15" s="12" t="n"/>
-      <c r="G15" s="12" t="n"/>
-      <c r="H15" s="13" t="inlineStr">
-        <is>
-          <t>(paste Google Sheets URL here)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>API Developer Agreement</t>
+          <t>Full-Time Employment Contract</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
@@ -867,16 +811,16 @@
     </row>
     <row r="17">
       <c r="A17" s="12" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Guarantor / Surety Form</t>
+          <t>Contract Worker Agreement</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Form</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="D17" s="12" t="n"/>
@@ -891,11 +835,11 @@
     </row>
     <row r="18">
       <c r="A18" s="10" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Non-Disclosure Agreement</t>
+          <t>Internship Agreement</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
@@ -915,16 +859,16 @@
     </row>
     <row r="19">
       <c r="A19" s="12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Candidate Application Form</t>
+          <t>Office Marketer Agreement</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>HR Form</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="D19" s="12" t="n"/>
@@ -939,16 +883,16 @@
     </row>
     <row r="20">
       <c r="A20" s="10" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Interview Process &amp; Checklist</t>
+          <t>Commission Marketer Agreement</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>HR Form</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="D20" s="10" t="n"/>
@@ -963,16 +907,16 @@
     </row>
     <row r="21">
       <c r="A21" s="12" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Leave Request Form</t>
+          <t>Installer Agreement</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>HR Form</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="D21" s="12" t="n"/>
@@ -987,16 +931,16 @@
     </row>
     <row r="22">
       <c r="A22" s="10" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Staff ID Card Request</t>
+          <t>API Developer Agreement</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>HR Form</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="D22" s="10" t="n"/>
@@ -1011,16 +955,16 @@
     </row>
     <row r="23">
       <c r="A23" s="12" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Job Requirements Handbook</t>
+          <t>Guarantor / Surety Form</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Form</t>
         </is>
       </c>
       <c r="D23" s="12" t="n"/>
@@ -1033,289 +977,469 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Non-Disclosure Agreement</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="n"/>
+      <c r="E24" s="10" t="n"/>
+      <c r="F24" s="10" t="n"/>
+      <c r="G24" s="10" t="n"/>
+      <c r="H24" s="11" t="inlineStr">
+        <is>
+          <t>(paste Google Sheets URL here)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>Candidate Application Form</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>HR Form</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="n"/>
+      <c r="E25" s="12" t="n"/>
+      <c r="F25" s="12" t="n"/>
+      <c r="G25" s="12" t="n"/>
+      <c r="H25" s="13" t="inlineStr">
+        <is>
+          <t>(paste Google Sheets URL here)</t>
+        </is>
+      </c>
+    </row>
     <row r="26" ht="26" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="A26" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>Interview Process &amp; Checklist</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>HR Form</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="n"/>
+      <c r="E26" s="10" t="n"/>
+      <c r="F26" s="10" t="n"/>
+      <c r="G26" s="10" t="n"/>
+      <c r="H26" s="11" t="inlineStr">
+        <is>
+          <t>(paste Google Sheets URL here)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>Leave Request Form</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>HR Form</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="n"/>
+      <c r="E27" s="12" t="n"/>
+      <c r="F27" s="12" t="n"/>
+      <c r="G27" s="12" t="n"/>
+      <c r="H27" s="13" t="inlineStr">
+        <is>
+          <t>(paste Google Sheets URL here)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Staff ID Card Request</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>HR Form</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="10" t="n"/>
+      <c r="F28" s="10" t="n"/>
+      <c r="G28" s="10" t="n"/>
+      <c r="H28" s="11" t="inlineStr">
+        <is>
+          <t>(paste Google Sheets URL here)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>Job Requirements Handbook</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="n"/>
+      <c r="E29" s="12" t="n"/>
+      <c r="F29" s="12" t="n"/>
+      <c r="G29" s="12" t="n"/>
+      <c r="H29" s="13" t="inlineStr">
+        <is>
+          <t>(paste Google Sheets URL here)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  TEAM SUMMARY (37 Roles: 24 FT + 5 Contract + 8 Intern)</t>
         </is>
       </c>
-      <c r="B26" s="8" t="n"/>
-      <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="n"/>
-      <c r="E26" s="8" t="n"/>
-      <c r="F26" s="8" t="n"/>
-      <c r="G26" s="8" t="n"/>
-      <c r="H26" s="8" t="n"/>
-    </row>
-    <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="9" t="inlineStr">
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B33" s="9" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C33" s="9" t="inlineStr">
         <is>
           <t>Target Count</t>
         </is>
       </c>
-      <c r="D27" s="9" t="inlineStr">
+      <c r="D33" s="9" t="inlineStr">
         <is>
           <t>Hired</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr">
+      <c r="E33" s="9" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
       </c>
-      <c r="F27" s="9" t="inlineStr">
+      <c r="F33" s="9" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="G27" s="9" t="inlineStr">
+      <c r="G33" s="9" t="inlineStr">
         <is>
           <t>% Complete</t>
         </is>
       </c>
-      <c r="H27" s="9" t="inlineStr">
+      <c r="H33" s="9" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="14" t="n">
+    <row r="34" ht="26" customHeight="1">
+      <c r="A34" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B28" s="14" t="inlineStr">
+      <c r="B34" s="14" t="inlineStr">
         <is>
           <t>Full-Time Employees</t>
         </is>
       </c>
-      <c r="C28" s="14" t="inlineStr">
+      <c r="C34" s="14" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D28" s="14" t="n"/>
-      <c r="E28" s="14" t="n"/>
-      <c r="F28" s="14" t="n"/>
-      <c r="G28" s="14" t="n"/>
-      <c r="H28" s="14" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="15" t="n">
+      <c r="D34" s="14" t="n"/>
+      <c r="E34" s="14" t="n"/>
+      <c r="F34" s="14" t="n"/>
+      <c r="G34" s="14" t="n"/>
+      <c r="H34" s="14" t="n"/>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="B35" s="15" t="inlineStr">
         <is>
           <t>Contract Workers</t>
         </is>
       </c>
-      <c r="C29" s="15" t="inlineStr">
+      <c r="C35" s="15" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D29" s="15" t="n"/>
-      <c r="E29" s="15" t="n"/>
-      <c r="F29" s="15" t="n"/>
-      <c r="G29" s="15" t="n"/>
-      <c r="H29" s="15" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="14" t="n">
+      <c r="D35" s="15" t="n"/>
+      <c r="E35" s="15" t="n"/>
+      <c r="F35" s="15" t="n"/>
+      <c r="G35" s="15" t="n"/>
+      <c r="H35" s="15" t="n"/>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="B30" s="14" t="inlineStr">
+      <c r="B36" s="14" t="inlineStr">
         <is>
           <t>Interns</t>
         </is>
       </c>
-      <c r="C30" s="14" t="inlineStr">
+      <c r="C36" s="14" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D30" s="14" t="n"/>
-      <c r="E30" s="14" t="n"/>
-      <c r="F30" s="14" t="n"/>
-      <c r="G30" s="14" t="n"/>
-      <c r="H30" s="14" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="16" t="n">
+      <c r="D36" s="14" t="n"/>
+      <c r="E36" s="14" t="n"/>
+      <c r="F36" s="14" t="n"/>
+      <c r="G36" s="14" t="n"/>
+      <c r="H36" s="14" t="n"/>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="B31" s="16" t="inlineStr">
+      <c r="B37" s="16" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C31" s="16" t="inlineStr">
+      <c r="C37" s="16" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D31" s="16" t="n"/>
-      <c r="E31" s="16" t="n"/>
-      <c r="F31" s="16" t="n"/>
-      <c r="G31" s="16" t="n"/>
-      <c r="H31" s="16" t="n"/>
-    </row>
-    <row r="34" ht="26" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
+      <c r="D37" s="16" t="n"/>
+      <c r="E37" s="16" t="n"/>
+      <c r="F37" s="16" t="n"/>
+      <c r="G37" s="16" t="n"/>
+      <c r="H37" s="16" t="n"/>
+    </row>
+    <row r="38" ht="20" customHeight="1"/>
+    <row r="39" ht="20" customHeight="1"/>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  GOOGLE SHEETS SETUP INSTRUCTIONS</t>
-        </is>
-      </c>
-      <c r="B34" s="8" t="n"/>
-      <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="n"/>
-      <c r="E34" s="8" t="n"/>
-      <c r="F34" s="8" t="n"/>
-      <c r="G34" s="8" t="n"/>
-      <c r="H34" s="8" t="n"/>
-    </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1. Open Google Drive (drive.google.com)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2. Click '+ New' &gt; 'File upload' &gt; Select the .xlsx file</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  3. Double-click the uploaded file to open in Google Sheets</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  4. Google Sheets will automatically convert the file</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  5. Click 'File' &gt; 'Save as Google Sheets' to create native version</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  6. Share via 'Share' button (top-right) with team members</t>
         </is>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  7. Set permissions: 'Editor' for HR, 'Viewer' for managers</t>
+          <t xml:space="preserve">  1. Open Google Drive (drive.google.com)</t>
         </is>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  8. Copy the sharing URL and paste in the 'Google Sheets Link' column above</t>
+          <t xml:space="preserve">  2. Click '+ New' &gt; 'File upload' &gt; Select the .xlsx file</t>
         </is>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  </t>
+          <t xml:space="preserve">  3. Double-click the uploaded file to open in Google Sheets</t>
         </is>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TIP: All dropdown validations and formatting will be preserved in Google Sheets!</t>
+          <t xml:space="preserve">  4. Google Sheets will automatically convert the file</t>
         </is>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="17" t="inlineStr">
         <is>
+          <t xml:space="preserve">  5. Click 'File' &gt; 'Save as Google Sheets' to create native version</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  6. Share via 'Share' button (top-right) with team members</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="3" customHeight="1">
+      <c r="A47" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  7. Set permissions: 'Editor' for HR, 'Viewer' for managers</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  8. Copy the sharing URL and paste in the 'Google Sheets Link' column above</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="3" customHeight="1">
+      <c r="A49" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  </t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  TIP: All dropdown validations and formatting will be preserved in Google Sheets!</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="17" t="inlineStr">
+        <is>
           <t xml:space="preserve">  TIP: Use 'File &gt; Make a copy' to create templates for new hires.</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="3" customHeight="1">
-      <c r="A47" s="5" t="n"/>
-      <c r="B47" s="5" t="n"/>
-      <c r="C47" s="5" t="n"/>
-      <c r="D47" s="5" t="n"/>
-      <c r="E47" s="5" t="n"/>
-      <c r="F47" s="5" t="n"/>
-      <c r="G47" s="5" t="n"/>
-      <c r="H47" s="5" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="18" t="inlineStr">
+    <row r="52"/>
+    <row r="53">
+      <c r="A53" s="5" t="n"/>
+      <c r="B53" s="5" t="n"/>
+      <c r="C53" s="5" t="n"/>
+      <c r="D53" s="5" t="n"/>
+      <c r="E53" s="5" t="n"/>
+      <c r="F53" s="5" t="n"/>
+      <c r="G53" s="5" t="n"/>
+      <c r="H53" s="5" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="18" t="inlineStr">
         <is>
           <t>PECH Group Holdings Ltd  |  Confidential  |  pechgroupholdings.tech  |  Technology &amp; Infrastructure Enablers for People</t>
         </is>
       </c>
-      <c r="B48" s="19" t="n"/>
-      <c r="C48" s="19" t="n"/>
-      <c r="D48" s="19" t="n"/>
-      <c r="E48" s="19" t="n"/>
-      <c r="F48" s="19" t="n"/>
-      <c r="G48" s="19" t="n"/>
-      <c r="H48" s="19" t="n"/>
-    </row>
-    <row r="49" ht="3" customHeight="1">
-      <c r="A49" s="1" t="n"/>
-      <c r="B49" s="1" t="n"/>
-      <c r="C49" s="1" t="n"/>
-      <c r="D49" s="1" t="n"/>
-      <c r="E49" s="1" t="n"/>
-      <c r="F49" s="1" t="n"/>
-      <c r="G49" s="1" t="n"/>
-      <c r="H49" s="1" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n"/>
+      <c r="B55" s="1" t="n"/>
+      <c r="C55" s="1" t="n"/>
+      <c r="D55" s="1" t="n"/>
+      <c r="E55" s="1" t="n"/>
+      <c r="F55" s="1" t="n"/>
+      <c r="G55" s="1" t="n"/>
+      <c r="H55" s="1" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="23" t="inlineStr">
+        <is>
+          <t>PECH GROUP HOLDINGS LTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="23" t="inlineStr">
+        <is>
+          <t>PECH GROUP HOLDINGS LTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="23" t="inlineStr">
+        <is>
+          <t>PECH GROUP HOLDINGS LTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="24" t="inlineStr">
+        <is>
+          <t>Confidential — PECH Group Holdings Ltd — Lagos, Nigeria — pechgroupholdings.tech</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n"/>
+      <c r="B61" s="1" t="n"/>
+      <c r="C61" s="1" t="n"/>
+      <c r="D61" s="1" t="n"/>
+      <c r="E61" s="1" t="n"/>
+      <c r="F61" s="1" t="n"/>
+      <c r="G61" s="1" t="n"/>
+      <c r="H61" s="1" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="23">
+    <mergeCell ref="A48:H48"/>
+    <mergeCell ref="A39:H39"/>
+    <mergeCell ref="A59:H59"/>
+    <mergeCell ref="A60:H60"/>
+    <mergeCell ref="A36:H36"/>
     <mergeCell ref="A45:H45"/>
-    <mergeCell ref="A48:H48"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="A37:H37"/>
     <mergeCell ref="A26:H26"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A39:H39"/>
+    <mergeCell ref="A57:H57"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A42:H42"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A8:H8"/>
     <mergeCell ref="A35:H35"/>
+    <mergeCell ref="A34:H34"/>
     <mergeCell ref="A43:H43"/>
     <mergeCell ref="A38:H38"/>
-    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A44:H44"/>
+    <mergeCell ref="A58:H58"/>
     <mergeCell ref="A40:H40"/>
-    <mergeCell ref="A42:H42"/>
-    <mergeCell ref="A41:H41"/>
-    <mergeCell ref="A36:H36"/>
-    <mergeCell ref="A44:H44"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A37:H37"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A34:H34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;8 PECH Group Holdings Ltd | Confidential</oddHeader>
+    <oddFooter>&amp;C&amp;7 PECH Group Holdings Ltd | Lagos, Nigeria | pechgroupholdings.tech</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/employment_xlsx/PECH_HR_MASTER_DASHBOARD.xlsx
+++ b/employment_xlsx/PECH_HR_MASTER_DASHBOARD.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -70,34 +70,6 @@
       <i val="1"/>
       <color rgb="00999999"/>
       <sz val="8"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="000099CC"/>
-      <sz val="18"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <i val="1"/>
-      <color rgb="00F5A623"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <color rgb="00888888"/>
-      <sz val="7"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="00E8F4F8"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <color rgb="00AAAAAA"/>
-      <sz val="7"/>
     </font>
   </fonts>
   <fills count="9">
@@ -176,7 +148,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -219,21 +191,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -308,36 +265,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1905000" cy="628650"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -629,7 +556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -642,31 +569,45 @@
     <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="20" t="inlineStr">
+    <row r="1" ht="6" customHeight="1">
+      <c r="A1" s="1" t="inlineStr"/>
+      <c r="B1" s="1" t="inlineStr"/>
+      <c r="C1" s="1" t="inlineStr"/>
+      <c r="D1" s="1" t="inlineStr"/>
+      <c r="E1" s="1" t="inlineStr"/>
+      <c r="F1" s="1" t="inlineStr"/>
+      <c r="G1" s="1" t="inlineStr"/>
+      <c r="H1" s="1" t="inlineStr"/>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>PECH GROUP HOLDINGS LTD</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="21" t="inlineStr">
-        <is>
-          <t>Technology &amp; Infrastructure Enablers for People</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="4" customHeight="1">
-      <c r="A3" s="1" t="n"/>
-      <c r="B3" s="1" t="n"/>
-      <c r="C3" s="1" t="n"/>
-      <c r="D3" s="1" t="n"/>
-      <c r="E3" s="1" t="n"/>
-      <c r="F3" s="1" t="n"/>
-      <c r="G3" s="1" t="n"/>
-      <c r="H3" s="1" t="n"/>
-    </row>
-    <row r="4" ht="2" customHeight="1">
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>PECH HR MASTER DASHBOARD</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4" ht="4" customHeight="1">
       <c r="A4" s="5" t="n"/>
       <c r="B4" s="5" t="n"/>
       <c r="C4" s="5" t="n"/>
@@ -676,122 +617,238 @@
       <c r="G4" s="5" t="n"/>
       <c r="H4" s="5" t="n"/>
     </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="22" t="inlineStr">
-        <is>
-          <t>Lagos, Nigeria  |  pechgroupholdings.tech  |  Confidential</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="8" customHeight="1"/>
-    <row r="7" ht="8" customHeight="1">
-      <c r="A7" s="1" t="inlineStr"/>
-      <c r="B7" s="1" t="inlineStr"/>
-      <c r="C7" s="1" t="inlineStr"/>
-      <c r="D7" s="1" t="inlineStr"/>
-      <c r="E7" s="1" t="inlineStr"/>
-      <c r="F7" s="1" t="inlineStr"/>
-      <c r="G7" s="1" t="inlineStr"/>
-      <c r="H7" s="1" t="inlineStr"/>
-    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Lagos, Nigeria  |  pechgroupholdings.tech  |  Employment Documents Overview  |  CONFIDENTIAL</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6" ht="4" customHeight="1">
+      <c r="A6" s="5" t="n"/>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="1" t="n"/>
+      <c r="F6" s="1" t="n"/>
+      <c r="G6" s="1" t="n"/>
+      <c r="H6" s="1" t="n"/>
+    </row>
+    <row r="7" ht="8" customHeight="1"/>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>PECH GROUP HOLDINGS LTD</t>
-        </is>
-      </c>
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  DOCUMENT INDEX &amp; STATUS</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="8" t="n"/>
+      <c r="H8" s="8" t="n"/>
     </row>
     <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>PECH HR MASTER DASHBOARD</t>
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Document Name</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>Total Records</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>Google Sheets Link</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
+      <c r="A10" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Full-Time Employment Contract</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="n"/>
+      <c r="E10" s="10" t="n"/>
+      <c r="F10" s="10" t="n"/>
+      <c r="G10" s="10" t="n"/>
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>(paste Google Sheets URL here)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Lagos, Nigeria  |  pechgroupholdings.tech  |  Employment Documents Overview  |  CONFIDENTIAL</t>
+      <c r="A11" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>Contract Worker Agreement</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="n"/>
+      <c r="E11" s="12" t="n"/>
+      <c r="F11" s="12" t="n"/>
+      <c r="G11" s="12" t="n"/>
+      <c r="H11" s="13" t="inlineStr">
+        <is>
+          <t>(paste Google Sheets URL here)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="1" t="n"/>
-      <c r="F12" s="1" t="n"/>
-      <c r="G12" s="1" t="n"/>
-      <c r="H12" s="1" t="n"/>
-    </row>
-    <row r="13"/>
+      <c r="A12" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Internship Agreement</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
+      <c r="G12" s="10" t="n"/>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>(paste Google Sheets URL here)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Office Marketer Agreement</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="n"/>
+      <c r="E13" s="12" t="n"/>
+      <c r="F13" s="12" t="n"/>
+      <c r="G13" s="12" t="n"/>
+      <c r="H13" s="13" t="inlineStr">
+        <is>
+          <t>(paste Google Sheets URL here)</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  DOCUMENT INDEX &amp; STATUS</t>
+      <c r="A14" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Commission Marketer Agreement</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
+      <c r="G14" s="10" t="n"/>
+      <c r="H14" s="11" t="inlineStr">
+        <is>
+          <t>(paste Google Sheets URL here)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>Document Name</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>Total Records</t>
-        </is>
-      </c>
-      <c r="E15" s="9" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="F15" s="9" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G15" s="9" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="H15" s="9" t="inlineStr">
-        <is>
-          <t>Google Sheets Link</t>
+      <c r="A15" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>Installer Agreement</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="n"/>
+      <c r="E15" s="12" t="n"/>
+      <c r="F15" s="12" t="n"/>
+      <c r="G15" s="12" t="n"/>
+      <c r="H15" s="13" t="inlineStr">
+        <is>
+          <t>(paste Google Sheets URL here)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Full-Time Employment Contract</t>
+          <t>API Developer Agreement</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
@@ -811,16 +868,16 @@
     </row>
     <row r="17">
       <c r="A17" s="12" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Contract Worker Agreement</t>
+          <t>Guarantor / Surety Form</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Contract</t>
+          <t>Form</t>
         </is>
       </c>
       <c r="D17" s="12" t="n"/>
@@ -835,11 +892,11 @@
     </row>
     <row r="18">
       <c r="A18" s="10" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Internship Agreement</t>
+          <t>Non-Disclosure Agreement</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
@@ -859,16 +916,16 @@
     </row>
     <row r="19">
       <c r="A19" s="12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Office Marketer Agreement</t>
+          <t>Candidate Application Form</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Contract</t>
+          <t>HR Form</t>
         </is>
       </c>
       <c r="D19" s="12" t="n"/>
@@ -883,16 +940,16 @@
     </row>
     <row r="20">
       <c r="A20" s="10" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Commission Marketer Agreement</t>
+          <t>Interview Process &amp; Checklist</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>Contract</t>
+          <t>HR Form</t>
         </is>
       </c>
       <c r="D20" s="10" t="n"/>
@@ -907,16 +964,16 @@
     </row>
     <row r="21">
       <c r="A21" s="12" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Installer Agreement</t>
+          <t>Leave Request Form</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Contract</t>
+          <t>HR Form</t>
         </is>
       </c>
       <c r="D21" s="12" t="n"/>
@@ -931,16 +988,16 @@
     </row>
     <row r="22">
       <c r="A22" s="10" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>API Developer Agreement</t>
+          <t>Staff ID Card Request</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>Contract</t>
+          <t>HR Form</t>
         </is>
       </c>
       <c r="D22" s="10" t="n"/>
@@ -955,16 +1012,16 @@
     </row>
     <row r="23">
       <c r="A23" s="12" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Guarantor / Surety Form</t>
+          <t>Job Requirements Handbook</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Form</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="D23" s="12" t="n"/>
@@ -977,469 +1034,289 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B24" s="10" t="inlineStr">
-        <is>
-          <t>Non-Disclosure Agreement</t>
-        </is>
-      </c>
-      <c r="C24" s="10" t="inlineStr">
-        <is>
-          <t>Contract</t>
-        </is>
-      </c>
-      <c r="D24" s="10" t="n"/>
-      <c r="E24" s="10" t="n"/>
-      <c r="F24" s="10" t="n"/>
-      <c r="G24" s="10" t="n"/>
-      <c r="H24" s="11" t="inlineStr">
-        <is>
-          <t>(paste Google Sheets URL here)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>Candidate Application Form</t>
-        </is>
-      </c>
-      <c r="C25" s="12" t="inlineStr">
-        <is>
-          <t>HR Form</t>
-        </is>
-      </c>
-      <c r="D25" s="12" t="n"/>
-      <c r="E25" s="12" t="n"/>
-      <c r="F25" s="12" t="n"/>
-      <c r="G25" s="12" t="n"/>
-      <c r="H25" s="13" t="inlineStr">
-        <is>
-          <t>(paste Google Sheets URL here)</t>
-        </is>
-      </c>
-    </row>
     <row r="26" ht="26" customHeight="1">
-      <c r="A26" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="B26" s="10" t="inlineStr">
-        <is>
-          <t>Interview Process &amp; Checklist</t>
-        </is>
-      </c>
-      <c r="C26" s="10" t="inlineStr">
-        <is>
-          <t>HR Form</t>
-        </is>
-      </c>
-      <c r="D26" s="10" t="n"/>
-      <c r="E26" s="10" t="n"/>
-      <c r="F26" s="10" t="n"/>
-      <c r="G26" s="10" t="n"/>
-      <c r="H26" s="11" t="inlineStr">
-        <is>
-          <t>(paste Google Sheets URL here)</t>
-        </is>
-      </c>
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  TEAM SUMMARY (37 Roles: 24 FT + 5 Contract + 8 Intern)</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="n"/>
+      <c r="C26" s="8" t="n"/>
+      <c r="D26" s="8" t="n"/>
+      <c r="E26" s="8" t="n"/>
+      <c r="F26" s="8" t="n"/>
+      <c r="G26" s="8" t="n"/>
+      <c r="H26" s="8" t="n"/>
     </row>
     <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="B27" s="12" t="inlineStr">
-        <is>
-          <t>Leave Request Form</t>
-        </is>
-      </c>
-      <c r="C27" s="12" t="inlineStr">
-        <is>
-          <t>HR Form</t>
-        </is>
-      </c>
-      <c r="D27" s="12" t="n"/>
-      <c r="E27" s="12" t="n"/>
-      <c r="F27" s="12" t="n"/>
-      <c r="G27" s="12" t="n"/>
-      <c r="H27" s="13" t="inlineStr">
-        <is>
-          <t>(paste Google Sheets URL here)</t>
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>Target Count</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>Hired</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G27" s="9" t="inlineStr">
+        <is>
+          <t>% Complete</t>
+        </is>
+      </c>
+      <c r="H27" s="9" t="inlineStr">
+        <is>
+          <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="n">
-        <v>13</v>
-      </c>
-      <c r="B28" s="10" t="inlineStr">
-        <is>
-          <t>Staff ID Card Request</t>
-        </is>
-      </c>
-      <c r="C28" s="10" t="inlineStr">
-        <is>
-          <t>HR Form</t>
-        </is>
-      </c>
-      <c r="D28" s="10" t="n"/>
-      <c r="E28" s="10" t="n"/>
-      <c r="F28" s="10" t="n"/>
-      <c r="G28" s="10" t="n"/>
-      <c r="H28" s="11" t="inlineStr">
-        <is>
-          <t>(paste Google Sheets URL here)</t>
-        </is>
-      </c>
+      <c r="A28" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>Full-Time Employees</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="n"/>
+      <c r="E28" s="14" t="n"/>
+      <c r="F28" s="14" t="n"/>
+      <c r="G28" s="14" t="n"/>
+      <c r="H28" s="14" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="B29" s="12" t="inlineStr">
-        <is>
-          <t>Job Requirements Handbook</t>
-        </is>
-      </c>
-      <c r="C29" s="12" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="D29" s="12" t="n"/>
-      <c r="E29" s="12" t="n"/>
-      <c r="F29" s="12" t="n"/>
-      <c r="G29" s="12" t="n"/>
-      <c r="H29" s="13" t="inlineStr">
-        <is>
-          <t>(paste Google Sheets URL here)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  TEAM SUMMARY (37 Roles: 24 FT + 5 Contract + 8 Intern)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="9" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B33" s="9" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="C33" s="9" t="inlineStr">
-        <is>
-          <t>Target Count</t>
-        </is>
-      </c>
-      <c r="D33" s="9" t="inlineStr">
-        <is>
-          <t>Hired</t>
-        </is>
-      </c>
-      <c r="E33" s="9" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="F33" s="9" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="G33" s="9" t="inlineStr">
-        <is>
-          <t>% Complete</t>
-        </is>
-      </c>
-      <c r="H33" s="9" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
+      <c r="A29" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t>Contract Workers</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="n"/>
+      <c r="E29" s="15" t="n"/>
+      <c r="F29" s="15" t="n"/>
+      <c r="G29" s="15" t="n"/>
+      <c r="H29" s="15" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>Interns</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="n"/>
+      <c r="E30" s="14" t="n"/>
+      <c r="F30" s="14" t="n"/>
+      <c r="G30" s="14" t="n"/>
+      <c r="H30" s="14" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="B31" s="16" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D31" s="16" t="n"/>
+      <c r="E31" s="16" t="n"/>
+      <c r="F31" s="16" t="n"/>
+      <c r="G31" s="16" t="n"/>
+      <c r="H31" s="16" t="n"/>
     </row>
     <row r="34" ht="26" customHeight="1">
-      <c r="A34" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="B34" s="14" t="inlineStr">
-        <is>
-          <t>Full-Time Employees</t>
-        </is>
-      </c>
-      <c r="C34" s="14" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="D34" s="14" t="n"/>
-      <c r="E34" s="14" t="n"/>
-      <c r="F34" s="14" t="n"/>
-      <c r="G34" s="14" t="n"/>
-      <c r="H34" s="14" t="n"/>
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  GOOGLE SHEETS SETUP INSTRUCTIONS</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="n"/>
+      <c r="C34" s="8" t="n"/>
+      <c r="D34" s="8" t="n"/>
+      <c r="E34" s="8" t="n"/>
+      <c r="F34" s="8" t="n"/>
+      <c r="G34" s="8" t="n"/>
+      <c r="H34" s="8" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="B35" s="15" t="inlineStr">
-        <is>
-          <t>Contract Workers</t>
-        </is>
-      </c>
-      <c r="C35" s="15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D35" s="15" t="n"/>
-      <c r="E35" s="15" t="n"/>
-      <c r="F35" s="15" t="n"/>
-      <c r="G35" s="15" t="n"/>
-      <c r="H35" s="15" t="n"/>
+      <c r="A35" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1. Open Google Drive (drive.google.com)</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="B36" s="14" t="inlineStr">
-        <is>
-          <t>Interns</t>
-        </is>
-      </c>
-      <c r="C36" s="14" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D36" s="14" t="n"/>
-      <c r="E36" s="14" t="n"/>
-      <c r="F36" s="14" t="n"/>
-      <c r="G36" s="14" t="n"/>
-      <c r="H36" s="14" t="n"/>
+      <c r="A36" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2. Click '+ New' &gt; 'File upload' &gt; Select the .xlsx file</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="B37" s="16" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C37" s="16" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="D37" s="16" t="n"/>
-      <c r="E37" s="16" t="n"/>
-      <c r="F37" s="16" t="n"/>
-      <c r="G37" s="16" t="n"/>
-      <c r="H37" s="16" t="n"/>
-    </row>
-    <row r="38" ht="20" customHeight="1"/>
-    <row r="39" ht="20" customHeight="1"/>
+      <c r="A37" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3. Double-click the uploaded file to open in Google Sheets</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4. Google Sheets will automatically convert the file</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5. Click 'File' &gt; 'Save as Google Sheets' to create native version</t>
+        </is>
+      </c>
+    </row>
     <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  GOOGLE SHEETS SETUP INSTRUCTIONS</t>
+      <c r="A40" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  6. Share via 'Share' button (top-right) with team members</t>
         </is>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1. Open Google Drive (drive.google.com)</t>
+          <t xml:space="preserve">  7. Set permissions: 'Editor' for HR, 'Viewer' for managers</t>
         </is>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2. Click '+ New' &gt; 'File upload' &gt; Select the .xlsx file</t>
+          <t xml:space="preserve">  8. Copy the sharing URL and paste in the 'Google Sheets Link' column above</t>
         </is>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3. Double-click the uploaded file to open in Google Sheets</t>
+          <t xml:space="preserve">  </t>
         </is>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4. Google Sheets will automatically convert the file</t>
+          <t xml:space="preserve">  TIP: All dropdown validations and formatting will be preserved in Google Sheets!</t>
         </is>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  5. Click 'File' &gt; 'Save as Google Sheets' to create native version</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  6. Share via 'Share' button (top-right) with team members</t>
+          <t xml:space="preserve">  TIP: Use 'File &gt; Make a copy' to create templates for new hires.</t>
         </is>
       </c>
     </row>
     <row r="47" ht="3" customHeight="1">
-      <c r="A47" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  7. Set permissions: 'Editor' for HR, 'Viewer' for managers</t>
-        </is>
-      </c>
+      <c r="A47" s="5" t="n"/>
+      <c r="B47" s="5" t="n"/>
+      <c r="C47" s="5" t="n"/>
+      <c r="D47" s="5" t="n"/>
+      <c r="E47" s="5" t="n"/>
+      <c r="F47" s="5" t="n"/>
+      <c r="G47" s="5" t="n"/>
+      <c r="H47" s="5" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  8. Copy the sharing URL and paste in the 'Google Sheets Link' column above</t>
-        </is>
-      </c>
+      <c r="A48" s="18" t="inlineStr">
+        <is>
+          <t>PECH Group Holdings Ltd  |  Confidential  |  pechgroupholdings.tech  |  Technology &amp; Infrastructure Enablers for People</t>
+        </is>
+      </c>
+      <c r="B48" s="19" t="n"/>
+      <c r="C48" s="19" t="n"/>
+      <c r="D48" s="19" t="n"/>
+      <c r="E48" s="19" t="n"/>
+      <c r="F48" s="19" t="n"/>
+      <c r="G48" s="19" t="n"/>
+      <c r="H48" s="19" t="n"/>
     </row>
     <row r="49" ht="3" customHeight="1">
-      <c r="A49" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  </t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  TIP: All dropdown validations and formatting will be preserved in Google Sheets!</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  TIP: Use 'File &gt; Make a copy' to create templates for new hires.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52"/>
-    <row r="53">
-      <c r="A53" s="5" t="n"/>
-      <c r="B53" s="5" t="n"/>
-      <c r="C53" s="5" t="n"/>
-      <c r="D53" s="5" t="n"/>
-      <c r="E53" s="5" t="n"/>
-      <c r="F53" s="5" t="n"/>
-      <c r="G53" s="5" t="n"/>
-      <c r="H53" s="5" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="18" t="inlineStr">
-        <is>
-          <t>PECH Group Holdings Ltd  |  Confidential  |  pechgroupholdings.tech  |  Technology &amp; Infrastructure Enablers for People</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="n"/>
-      <c r="B55" s="1" t="n"/>
-      <c r="C55" s="1" t="n"/>
-      <c r="D55" s="1" t="n"/>
-      <c r="E55" s="1" t="n"/>
-      <c r="F55" s="1" t="n"/>
-      <c r="G55" s="1" t="n"/>
-      <c r="H55" s="1" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="23" t="inlineStr">
-        <is>
-          <t>PECH GROUP HOLDINGS LTD</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="23" t="inlineStr">
-        <is>
-          <t>PECH GROUP HOLDINGS LTD</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="23" t="inlineStr">
-        <is>
-          <t>PECH GROUP HOLDINGS LTD</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="24" t="inlineStr">
-        <is>
-          <t>Confidential — PECH Group Holdings Ltd — Lagos, Nigeria — pechgroupholdings.tech</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="1" t="n"/>
-      <c r="B61" s="1" t="n"/>
-      <c r="C61" s="1" t="n"/>
-      <c r="D61" s="1" t="n"/>
-      <c r="E61" s="1" t="n"/>
-      <c r="F61" s="1" t="n"/>
-      <c r="G61" s="1" t="n"/>
-      <c r="H61" s="1" t="n"/>
+      <c r="A49" s="1" t="n"/>
+      <c r="B49" s="1" t="n"/>
+      <c r="C49" s="1" t="n"/>
+      <c r="D49" s="1" t="n"/>
+      <c r="E49" s="1" t="n"/>
+      <c r="F49" s="1" t="n"/>
+      <c r="G49" s="1" t="n"/>
+      <c r="H49" s="1" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="18">
+    <mergeCell ref="A45:H45"/>
     <mergeCell ref="A48:H48"/>
-    <mergeCell ref="A39:H39"/>
-    <mergeCell ref="A59:H59"/>
-    <mergeCell ref="A60:H60"/>
-    <mergeCell ref="A36:H36"/>
-    <mergeCell ref="A45:H45"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A41:H41"/>
-    <mergeCell ref="A37:H37"/>
     <mergeCell ref="A26:H26"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A57:H57"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A42:H42"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A39:H39"/>
     <mergeCell ref="A35:H35"/>
-    <mergeCell ref="A34:H34"/>
     <mergeCell ref="A43:H43"/>
     <mergeCell ref="A38:H38"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A40:H40"/>
+    <mergeCell ref="A42:H42"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="A36:H36"/>
     <mergeCell ref="A44:H44"/>
-    <mergeCell ref="A58:H58"/>
-    <mergeCell ref="A40:H40"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A34:H34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader>&amp;C&amp;8 PECH Group Holdings Ltd | Confidential</oddHeader>
-    <oddFooter>&amp;C&amp;7 PECH Group Holdings Ltd | Lagos, Nigeria | pechgroupholdings.tech</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/employment_xlsx/PECH_HR_MASTER_DASHBOARD.xlsx
+++ b/employment_xlsx/PECH_HR_MASTER_DASHBOARD.xlsx
@@ -99,14 +99,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000099CC"/>
-        <bgColor rgb="000099CC"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="000099CC"/>
+        <bgColor rgb="000099CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -122,13 +122,19 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
     </border>
     <border>
       <left style="thin">
@@ -148,49 +154,49 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -641,621 +647,630 @@
       <c r="G6" s="1" t="n"/>
       <c r="H6" s="1" t="n"/>
     </row>
-    <row r="7" ht="8" customHeight="1"/>
+    <row r="7" ht="8" customHeight="1">
+      <c r="A7" s="7" t="n"/>
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="7" t="n"/>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="7" t="n"/>
+      <c r="H7" s="7" t="n"/>
+    </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">  DOCUMENT INDEX &amp; STATUS</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n"/>
-      <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="n"/>
-      <c r="E8" s="8" t="n"/>
-      <c r="F8" s="8" t="n"/>
-      <c r="G8" s="8" t="n"/>
-      <c r="H8" s="8" t="n"/>
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="9" t="n"/>
+      <c r="G8" s="9" t="n"/>
+      <c r="H8" s="9" t="n"/>
     </row>
     <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>Document Name</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>Total Records</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="F9" s="9" t="inlineStr">
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="H9" s="9" t="inlineStr">
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>Google Sheets Link</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="10" t="n">
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>Full-Time Employment Contract</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
       </c>
-      <c r="D10" s="10" t="n"/>
-      <c r="E10" s="10" t="n"/>
-      <c r="F10" s="10" t="n"/>
-      <c r="G10" s="10" t="n"/>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="D10" s="11" t="n"/>
+      <c r="E10" s="11" t="n"/>
+      <c r="F10" s="11" t="n"/>
+      <c r="G10" s="11" t="n"/>
+      <c r="H10" s="12" t="inlineStr">
         <is>
           <t>(paste Google Sheets URL here)</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="12" t="n">
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>Contract Worker Agreement</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
       </c>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="12" t="n"/>
-      <c r="F11" s="12" t="n"/>
-      <c r="G11" s="12" t="n"/>
-      <c r="H11" s="13" t="inlineStr">
+      <c r="D11" s="13" t="n"/>
+      <c r="E11" s="13" t="n"/>
+      <c r="F11" s="13" t="n"/>
+      <c r="G11" s="13" t="n"/>
+      <c r="H11" s="14" t="inlineStr">
         <is>
           <t>(paste Google Sheets URL here)</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="10" t="n">
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>Internship Agreement</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
       </c>
-      <c r="D12" s="10" t="n"/>
-      <c r="E12" s="10" t="n"/>
-      <c r="F12" s="10" t="n"/>
-      <c r="G12" s="10" t="n"/>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="D12" s="11" t="n"/>
+      <c r="E12" s="11" t="n"/>
+      <c r="F12" s="11" t="n"/>
+      <c r="G12" s="11" t="n"/>
+      <c r="H12" s="12" t="inlineStr">
         <is>
           <t>(paste Google Sheets URL here)</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="12" t="n">
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>Office Marketer Agreement</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
       </c>
-      <c r="D13" s="12" t="n"/>
-      <c r="E13" s="12" t="n"/>
-      <c r="F13" s="12" t="n"/>
-      <c r="G13" s="12" t="n"/>
-      <c r="H13" s="13" t="inlineStr">
+      <c r="D13" s="13" t="n"/>
+      <c r="E13" s="13" t="n"/>
+      <c r="F13" s="13" t="n"/>
+      <c r="G13" s="13" t="n"/>
+      <c r="H13" s="14" t="inlineStr">
         <is>
           <t>(paste Google Sheets URL here)</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="10" t="n">
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>Commission Marketer Agreement</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
       </c>
-      <c r="D14" s="10" t="n"/>
-      <c r="E14" s="10" t="n"/>
-      <c r="F14" s="10" t="n"/>
-      <c r="G14" s="10" t="n"/>
-      <c r="H14" s="11" t="inlineStr">
+      <c r="D14" s="11" t="n"/>
+      <c r="E14" s="11" t="n"/>
+      <c r="F14" s="11" t="n"/>
+      <c r="G14" s="11" t="n"/>
+      <c r="H14" s="12" t="inlineStr">
         <is>
           <t>(paste Google Sheets URL here)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="12" t="n">
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>Installer Agreement</t>
         </is>
       </c>
-      <c r="C15" s="12" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
       </c>
-      <c r="D15" s="12" t="n"/>
-      <c r="E15" s="12" t="n"/>
-      <c r="F15" s="12" t="n"/>
-      <c r="G15" s="12" t="n"/>
-      <c r="H15" s="13" t="inlineStr">
+      <c r="D15" s="13" t="n"/>
+      <c r="E15" s="13" t="n"/>
+      <c r="F15" s="13" t="n"/>
+      <c r="G15" s="13" t="n"/>
+      <c r="H15" s="14" t="inlineStr">
         <is>
           <t>(paste Google Sheets URL here)</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="10" t="n">
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>API Developer Agreement</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
       </c>
-      <c r="D16" s="10" t="n"/>
-      <c r="E16" s="10" t="n"/>
-      <c r="F16" s="10" t="n"/>
-      <c r="G16" s="10" t="n"/>
-      <c r="H16" s="11" t="inlineStr">
+      <c r="D16" s="11" t="n"/>
+      <c r="E16" s="11" t="n"/>
+      <c r="F16" s="11" t="n"/>
+      <c r="G16" s="11" t="n"/>
+      <c r="H16" s="12" t="inlineStr">
         <is>
           <t>(paste Google Sheets URL here)</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="12" t="n">
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B17" s="13" t="inlineStr">
         <is>
           <t>Guarantor / Surety Form</t>
         </is>
       </c>
-      <c r="C17" s="12" t="inlineStr">
+      <c r="C17" s="13" t="inlineStr">
         <is>
           <t>Form</t>
         </is>
       </c>
-      <c r="D17" s="12" t="n"/>
-      <c r="E17" s="12" t="n"/>
-      <c r="F17" s="12" t="n"/>
-      <c r="G17" s="12" t="n"/>
-      <c r="H17" s="13" t="inlineStr">
+      <c r="D17" s="13" t="n"/>
+      <c r="E17" s="13" t="n"/>
+      <c r="F17" s="13" t="n"/>
+      <c r="G17" s="13" t="n"/>
+      <c r="H17" s="14" t="inlineStr">
         <is>
           <t>(paste Google Sheets URL here)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="10" t="n">
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>Non-Disclosure Agreement</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
       </c>
-      <c r="D18" s="10" t="n"/>
-      <c r="E18" s="10" t="n"/>
-      <c r="F18" s="10" t="n"/>
-      <c r="G18" s="10" t="n"/>
-      <c r="H18" s="11" t="inlineStr">
+      <c r="D18" s="11" t="n"/>
+      <c r="E18" s="11" t="n"/>
+      <c r="F18" s="11" t="n"/>
+      <c r="G18" s="11" t="n"/>
+      <c r="H18" s="12" t="inlineStr">
         <is>
           <t>(paste Google Sheets URL here)</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="12" t="n">
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B19" s="13" t="inlineStr">
         <is>
           <t>Candidate Application Form</t>
         </is>
       </c>
-      <c r="C19" s="12" t="inlineStr">
+      <c r="C19" s="13" t="inlineStr">
         <is>
           <t>HR Form</t>
         </is>
       </c>
-      <c r="D19" s="12" t="n"/>
-      <c r="E19" s="12" t="n"/>
-      <c r="F19" s="12" t="n"/>
-      <c r="G19" s="12" t="n"/>
-      <c r="H19" s="13" t="inlineStr">
+      <c r="D19" s="13" t="n"/>
+      <c r="E19" s="13" t="n"/>
+      <c r="F19" s="13" t="n"/>
+      <c r="G19" s="13" t="n"/>
+      <c r="H19" s="14" t="inlineStr">
         <is>
           <t>(paste Google Sheets URL here)</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="10" t="n">
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>Interview Process &amp; Checklist</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="11" t="inlineStr">
         <is>
           <t>HR Form</t>
         </is>
       </c>
-      <c r="D20" s="10" t="n"/>
-      <c r="E20" s="10" t="n"/>
-      <c r="F20" s="10" t="n"/>
-      <c r="G20" s="10" t="n"/>
-      <c r="H20" s="11" t="inlineStr">
+      <c r="D20" s="11" t="n"/>
+      <c r="E20" s="11" t="n"/>
+      <c r="F20" s="11" t="n"/>
+      <c r="G20" s="11" t="n"/>
+      <c r="H20" s="12" t="inlineStr">
         <is>
           <t>(paste Google Sheets URL here)</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="12" t="n">
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B21" s="13" t="inlineStr">
         <is>
           <t>Leave Request Form</t>
         </is>
       </c>
-      <c r="C21" s="12" t="inlineStr">
+      <c r="C21" s="13" t="inlineStr">
         <is>
           <t>HR Form</t>
         </is>
       </c>
-      <c r="D21" s="12" t="n"/>
-      <c r="E21" s="12" t="n"/>
-      <c r="F21" s="12" t="n"/>
-      <c r="G21" s="12" t="n"/>
-      <c r="H21" s="13" t="inlineStr">
+      <c r="D21" s="13" t="n"/>
+      <c r="E21" s="13" t="n"/>
+      <c r="F21" s="13" t="n"/>
+      <c r="G21" s="13" t="n"/>
+      <c r="H21" s="14" t="inlineStr">
         <is>
           <t>(paste Google Sheets URL here)</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="10" t="n">
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>Staff ID Card Request</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>HR Form</t>
         </is>
       </c>
-      <c r="D22" s="10" t="n"/>
-      <c r="E22" s="10" t="n"/>
-      <c r="F22" s="10" t="n"/>
-      <c r="G22" s="10" t="n"/>
-      <c r="H22" s="11" t="inlineStr">
+      <c r="D22" s="11" t="n"/>
+      <c r="E22" s="11" t="n"/>
+      <c r="F22" s="11" t="n"/>
+      <c r="G22" s="11" t="n"/>
+      <c r="H22" s="12" t="inlineStr">
         <is>
           <t>(paste Google Sheets URL here)</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="12" t="n">
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="13" t="n">
         <v>14</v>
       </c>
-      <c r="B23" s="12" t="inlineStr">
+      <c r="B23" s="13" t="inlineStr">
         <is>
           <t>Job Requirements Handbook</t>
         </is>
       </c>
-      <c r="C23" s="12" t="inlineStr">
+      <c r="C23" s="13" t="inlineStr">
         <is>
           <t>Reference</t>
         </is>
       </c>
-      <c r="D23" s="12" t="n"/>
-      <c r="E23" s="12" t="n"/>
-      <c r="F23" s="12" t="n"/>
-      <c r="G23" s="12" t="n"/>
-      <c r="H23" s="13" t="inlineStr">
+      <c r="D23" s="13" t="n"/>
+      <c r="E23" s="13" t="n"/>
+      <c r="F23" s="13" t="n"/>
+      <c r="G23" s="13" t="n"/>
+      <c r="H23" s="14" t="inlineStr">
         <is>
           <t>(paste Google Sheets URL here)</t>
         </is>
       </c>
     </row>
     <row r="26" ht="26" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">  TEAM SUMMARY (37 Roles: 24 FT + 5 Contract + 8 Intern)</t>
         </is>
       </c>
-      <c r="B26" s="8" t="n"/>
-      <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="n"/>
-      <c r="E26" s="8" t="n"/>
-      <c r="F26" s="8" t="n"/>
-      <c r="G26" s="8" t="n"/>
-      <c r="H26" s="8" t="n"/>
+      <c r="B26" s="9" t="n"/>
+      <c r="C26" s="9" t="n"/>
+      <c r="D26" s="9" t="n"/>
+      <c r="E26" s="9" t="n"/>
+      <c r="F26" s="9" t="n"/>
+      <c r="G26" s="9" t="n"/>
+      <c r="H26" s="9" t="n"/>
     </row>
     <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B27" s="10" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C27" s="10" t="inlineStr">
         <is>
           <t>Target Count</t>
         </is>
       </c>
-      <c r="D27" s="9" t="inlineStr">
+      <c r="D27" s="10" t="inlineStr">
         <is>
           <t>Hired</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr">
+      <c r="E27" s="10" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
       </c>
-      <c r="F27" s="9" t="inlineStr">
+      <c r="F27" s="10" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="G27" s="9" t="inlineStr">
+      <c r="G27" s="10" t="inlineStr">
         <is>
           <t>% Complete</t>
         </is>
       </c>
-      <c r="H27" s="9" t="inlineStr">
+      <c r="H27" s="10" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="14" t="n">
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="B28" s="14" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t>Full-Time Employees</t>
         </is>
       </c>
-      <c r="C28" s="14" t="inlineStr">
+      <c r="C28" s="11" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D28" s="14" t="n"/>
-      <c r="E28" s="14" t="n"/>
-      <c r="F28" s="14" t="n"/>
-      <c r="G28" s="14" t="n"/>
-      <c r="H28" s="14" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="15" t="n">
+      <c r="D28" s="11" t="n"/>
+      <c r="E28" s="11" t="n"/>
+      <c r="F28" s="11" t="n"/>
+      <c r="G28" s="11" t="n"/>
+      <c r="H28" s="11" t="n"/>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="B29" s="13" t="inlineStr">
         <is>
           <t>Contract Workers</t>
         </is>
       </c>
-      <c r="C29" s="15" t="inlineStr">
+      <c r="C29" s="13" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D29" s="15" t="n"/>
-      <c r="E29" s="15" t="n"/>
-      <c r="F29" s="15" t="n"/>
-      <c r="G29" s="15" t="n"/>
-      <c r="H29" s="15" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="14" t="n">
+      <c r="D29" s="13" t="n"/>
+      <c r="E29" s="13" t="n"/>
+      <c r="F29" s="13" t="n"/>
+      <c r="G29" s="13" t="n"/>
+      <c r="H29" s="13" t="n"/>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="B30" s="14" t="inlineStr">
+      <c r="B30" s="11" t="inlineStr">
         <is>
           <t>Interns</t>
         </is>
       </c>
-      <c r="C30" s="14" t="inlineStr">
+      <c r="C30" s="11" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D30" s="14" t="n"/>
-      <c r="E30" s="14" t="n"/>
-      <c r="F30" s="14" t="n"/>
-      <c r="G30" s="14" t="n"/>
-      <c r="H30" s="14" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="16" t="n">
+      <c r="D30" s="11" t="n"/>
+      <c r="E30" s="11" t="n"/>
+      <c r="F30" s="11" t="n"/>
+      <c r="G30" s="11" t="n"/>
+      <c r="H30" s="11" t="n"/>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="B31" s="16" t="inlineStr">
+      <c r="B31" s="15" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C31" s="16" t="inlineStr">
+      <c r="C31" s="15" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D31" s="16" t="n"/>
-      <c r="E31" s="16" t="n"/>
-      <c r="F31" s="16" t="n"/>
-      <c r="G31" s="16" t="n"/>
-      <c r="H31" s="16" t="n"/>
+      <c r="D31" s="15" t="n"/>
+      <c r="E31" s="15" t="n"/>
+      <c r="F31" s="15" t="n"/>
+      <c r="G31" s="15" t="n"/>
+      <c r="H31" s="15" t="n"/>
     </row>
     <row r="34" ht="26" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">  GOOGLE SHEETS SETUP INSTRUCTIONS</t>
         </is>
       </c>
-      <c r="B34" s="8" t="n"/>
-      <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="n"/>
-      <c r="E34" s="8" t="n"/>
-      <c r="F34" s="8" t="n"/>
-      <c r="G34" s="8" t="n"/>
-      <c r="H34" s="8" t="n"/>
+      <c r="B34" s="9" t="n"/>
+      <c r="C34" s="9" t="n"/>
+      <c r="D34" s="9" t="n"/>
+      <c r="E34" s="9" t="n"/>
+      <c r="F34" s="9" t="n"/>
+      <c r="G34" s="9" t="n"/>
+      <c r="H34" s="9" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="17" t="inlineStr">
+      <c r="A35" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  1. Open Google Drive (drive.google.com)</t>
         </is>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="17" t="inlineStr">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  2. Click '+ New' &gt; 'File upload' &gt; Select the .xlsx file</t>
         </is>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="17" t="inlineStr">
+      <c r="A37" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  3. Double-click the uploaded file to open in Google Sheets</t>
         </is>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="17" t="inlineStr">
+      <c r="A38" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  4. Google Sheets will automatically convert the file</t>
         </is>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="17" t="inlineStr">
+      <c r="A39" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  5. Click 'File' &gt; 'Save as Google Sheets' to create native version</t>
         </is>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="17" t="inlineStr">
+      <c r="A40" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  6. Share via 'Share' button (top-right) with team members</t>
         </is>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="17" t="inlineStr">
+      <c r="A41" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  7. Set permissions: 'Editor' for HR, 'Viewer' for managers</t>
         </is>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="17" t="inlineStr">
+      <c r="A42" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  8. Copy the sharing URL and paste in the 'Google Sheets Link' column above</t>
         </is>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="17" t="inlineStr">
+      <c r="A43" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  </t>
         </is>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="17" t="inlineStr">
+      <c r="A44" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TIP: All dropdown validations and formatting will be preserved in Google Sheets!</t>
         </is>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="17" t="inlineStr">
+      <c r="A45" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TIP: Use 'File &gt; Make a copy' to create templates for new hires.</t>
         </is>
@@ -1271,19 +1286,19 @@
       <c r="G47" s="5" t="n"/>
       <c r="H47" s="5" t="n"/>
     </row>
-    <row r="48">
-      <c r="A48" s="18" t="inlineStr">
-        <is>
-          <t>PECH Group Holdings Ltd  |  Confidential  |  pechgroupholdings.tech  |  Technology &amp; Infrastructure Enablers for People</t>
-        </is>
-      </c>
-      <c r="B48" s="19" t="n"/>
-      <c r="C48" s="19" t="n"/>
-      <c r="D48" s="19" t="n"/>
-      <c r="E48" s="19" t="n"/>
-      <c r="F48" s="19" t="n"/>
-      <c r="G48" s="19" t="n"/>
-      <c r="H48" s="19" t="n"/>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="17" t="inlineStr">
+        <is>
+          <t>Confidential  |  pechgroupholdings.tech  |  Technology &amp; Infrastructure Enablers for People</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="n"/>
+      <c r="C48" s="7" t="n"/>
+      <c r="D48" s="7" t="n"/>
+      <c r="E48" s="7" t="n"/>
+      <c r="F48" s="7" t="n"/>
+      <c r="G48" s="7" t="n"/>
+      <c r="H48" s="7" t="n"/>
     </row>
     <row r="49" ht="3" customHeight="1">
       <c r="A49" s="1" t="n"/>
